--- a/s-s-event-bogor/sessions/clinic/services/services_account_template.xlsx
+++ b/s-s-event-bogor/sessions/clinic/services/services_account_template.xlsx
@@ -7,9 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physical Supply" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monetary Supply" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Part A - Physical Supply" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Part B - Monetary Supply" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carbon Calculator" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Rent Calculator" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +34,11 @@
       <b val="1"/>
       <color rgb="000A5455"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="003B9C7B"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -115,31 +122,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -506,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -515,174 +524,213 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SEEA EA Ecosystem Service Supply Account</t>
+          <t>SEEA EA Ecosystem Service Account -- Part A: Physical Supply</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Part A is a complete account on its own. Monetary valuation (Part B) is optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>Accounting area:</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Accounting year:</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Coral reefs</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Seagrass</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Mangroves</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Fish provisioning</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>kg/yr</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="8">
-        <f>SUM(C6:E6)</f>
-        <v/>
-      </c>
+      <c r="B5" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Coral reefs</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Seagrass</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Mangroves</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Fish provisioning</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>kg/yr</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="9">
+        <f>SUM(C8:F8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
           <t>Carbon sequestration</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Mg CO2/yr</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="8">
-        <f>SUM(C7:E7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="9">
+        <f>SUM(C9:F9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Coastal protection</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>m coastline</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="8">
-        <f>SUM(C8:E8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="9">
+        <f>SUM(C10:F10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Nursery habitat</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>kg biomass/yr</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="8">
-        <f>SUM(C9:E9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="9">
+        <f>SUM(C11:F11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Recreation</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>visitors/yr</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="8">
-        <f>SUM(C10:E10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="9">
+        <f>SUM(C12:F12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Gleaning</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>hours/yr</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="8">
-        <f>SUM(C11:E11)</f>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="9">
+        <f>SUM(C13:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Gleaning harvest</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>kg/yr</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="9">
+        <f>SUM(C14:F14)</f>
         <v/>
       </c>
     </row>
@@ -698,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -707,182 +755,242 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Monetary Ecosystem Service Supply (USD/yr)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Valuation method</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Coral reefs</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Seagrass</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Mangroves</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Total</t>
+          <t>SEEA EA Ecosystem Service Account -- Part B: Monetary Supply (USD/yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Part B builds on Part A. Only fill in services where you have economic data.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Valuation method</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Value type</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Coral reefs</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Seagrass</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Mangroves</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
           <t>Fish provisioning</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Resource rent</t>
         </is>
       </c>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="8">
-        <f>SUM(C4:E4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="9">
+        <f>SUM(D5:G5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Carbon sequestration</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Social cost of carbon</t>
         </is>
       </c>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="8">
-        <f>SUM(C5:E5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Non-market</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="9">
+        <f>SUM(D6:G6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Coastal protection</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Replacement cost</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="8">
-        <f>SUM(C6:E6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Non-market</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="9">
+        <f>SUM(D7:G7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Nursery habitat</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Productivity change</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="8">
-        <f>SUM(C7:E7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Market (indirect)</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="9">
+        <f>SUM(D8:G8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Recreation</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Direct expenditure</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="8">
-        <f>SUM(C8:E8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+      <c r="H9" s="9">
+        <f>SUM(D9:G9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Gleaning</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Equivalent wage</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="8">
-        <f>SUM(C9:E9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Equivalent wage + market</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="9">
+        <f>SUM(D10:G10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="9">
-        <f>SUM(C4:C9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="9">
-        <f>SUM(D4:D9)</f>
-        <v/>
-      </c>
-      <c r="E10" s="9">
-        <f>SUM(E4:E9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="9">
-        <f>SUM(F4:F9)</f>
+      <c r="B11" s="7" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="10">
+        <f>SUM(D5:D10)</f>
+        <v/>
+      </c>
+      <c r="E11" s="10">
+        <f>SUM(E5:E10)</f>
+        <v/>
+      </c>
+      <c r="F11" s="10">
+        <f>SUM(F5:F10)</f>
+        <v/>
+      </c>
+      <c r="G11" s="10">
+        <f>SUM(G5:G10)</f>
+        <v/>
+      </c>
+      <c r="H11" s="10">
+        <f>SUM(H5:H10)</f>
         <v/>
       </c>
     </row>
@@ -897,197 +1005,441 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Quick Calculation Helpers</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
           <t>Carbon Sequestration Calculator</t>
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Part A: fill extent and NCP rate. Part B: set carbon price.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Part A: Physical Quantification</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Ecosystem</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Extent (ha)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>NCP rate
 (Mg CO2/ha/yr)</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Physical supply
 (Mg CO2/yr)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Mangroves</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D6" s="9">
+        <f>B6*C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Seagrass</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D7" s="9">
+        <f>B7*C7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D8" s="10">
+        <f>D6+D7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Part B: Monetary Valuation</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Ecosystem</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Physical supply
+(Mg CO2/yr)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Carbon price
 (USD/Mg CO2)</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Value
 (USD/yr)</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Mangroves</t>
+        </is>
+      </c>
+      <c r="B12" s="9">
+        <f>D6</f>
+        <v/>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="D12" s="9">
+        <f>B12*C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Seagrass</t>
+        </is>
+      </c>
+      <c r="B13" s="9">
+        <f>D7</f>
+        <v/>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="D13" s="9">
+        <f>B13*C13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D14" s="10">
+        <f>D12+D13</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fish Provisioning -- Resource Rent Calculator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Part A: Physical Quantification</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Total catch (kg/yr)</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n"/>
+    </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Mangroves</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D5" s="8">
-        <f>B5*C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="F5" s="8">
-        <f>D5*E5</f>
-        <v/>
-      </c>
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Catch by species 1 (kg/yr)</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Seagrass</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D6" s="8">
-        <f>B6*C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="F6" s="8">
-        <f>D6*E6</f>
-        <v/>
-      </c>
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Catch by species 2 (kg/yr)</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Catch by species 3 (kg/yr)</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Resource Rent Calculator (Fish Provisioning)</t>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Part B: Monetary Valuation (Resource Rent)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>Total catch (kg/yr)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n"/>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Average price (USD/kg)</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Average price (USD/kg)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n"/>
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Gross revenue (USD/yr)</t>
+        </is>
+      </c>
+      <c r="B11" s="8">
+        <f>B4*B10</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Gross revenue (USD/yr)</t>
-        </is>
-      </c>
-      <c r="B12" s="7">
-        <f>B10*B11</f>
-        <v/>
-      </c>
+      <c r="A12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Labour costs (USD/yr)</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
+      <c r="B13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Fuel costs (USD/yr)</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n"/>
+      <c r="B14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Gear and maintenance (USD/yr)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
+      <c r="B15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Capital depreciation (USD/yr)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n"/>
+      <c r="B16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Total costs (USD/yr)</t>
         </is>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="8">
         <f>SUM(B13:B16)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Resource rent (USD/yr)</t>
         </is>
       </c>
-      <c r="B18" s="7">
-        <f>MAX(B12-B17,0)</f>
-        <v/>
+      <c r="B19" s="8">
+        <f>MAX(B11-B17,0)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>How to use this template</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>This workbook has two main sheets:</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Part A - Physical Supply: quantify services in physical units (kg, Mg CO2, visitors, m).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   This is a complete account on its own. Fill yellow cells with your data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Part B - Monetary Supply: assign economic values (USD/yr) to physical quantities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Requires Part A first. Only fill in services where you have economic data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   It is normal to have Part B for some services and not others.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Calculator sheets:</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Carbon Calculator: enter extent and NCP rate (Part A), then set carbon price (Part B).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Resource Rent Calculator: enter catch (Part A), then prices and costs (Part B).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Yellow cells are for your input. White cells with formulas calculate automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Adapt ecosystem type names and add columns as needed for your area.</t>
+        </is>
       </c>
     </row>
   </sheetData>
